--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_60.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_60.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C528DA78-6343-4393-B83D-02B3B1AA1469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5FF19A1-4782-4A88-B14E-50A970A9030A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -741,13 +741,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S01aH06,S02aH03,S05aH07,S05aH08,S04aH05,S04aH08,S03aH03,S04aH03,S03aH02,S04aH06,S05aH04,S06aH02,S06aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S04aH02,S01aH02,S04aH04,S03aH04,S01aH03,S05aH02,S05aH03,S05aH06,S02aH04,S02aH05,S06aH07,S01aH04,S01aH07,S02aH07,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S02aH02,S06aH06</t>
+    <t>S03aH04,S03aH03,S04aH02,S05aH08,S01aH04,S01aH07,S02aH07,S02aH04,S02aH05,S06aH07,S01aH06,S02aH03,S05aH07,S03aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S04aH03,S04aH05,S04aH08,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S02aH02,S06aH06,S01aH03,S05aH02,S05aH03,S05aH06,S04aH06,S05aH04,S06aH02,S06aH03,S01aH02,S04aH04</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S01aH01,S04aH01,S06aH02,S04aH08,S06aH01,S05aH08,S02aH02,S04aH10,S06aH10,S02aH01,S02aH10,S05aH02,S04aH02,S06aH09,S01aH02,S05aH10,S01aH10,S03aH02,S01aH08,S02aH08,S02aH09,S04aH09,S05aH01,S03aH08,S03aH10,S06aH08,S01aH09,S03aH09,S05aH09,S03aH01</t>
+    <t>S02aH09,S04aH09,S05aH01,S02aH02,S04aH10,S06aH10,S01aH10,S03aH02,S04aH08,S06aH01,S01aH09,S03aH08,S03aH10,S06aH08,S01aH01,S04aH01,S06aH02,S04aH02,S01aH02,S05aH10,S02aH01,S02aH10,S05aH02,S05aH08,S03aH09,S05aH09,S03aH01,S06aH09,S01aH08,S02aH08</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S01aH01,S04aH01,S06aH02,S04aH08,S06aH01,S05aH08,S02aH02,S04aH10,S06aH10,S02aH01,S02aH10,S05aH02,S04aH02,S06aH09,S01aH02,S05aH10,S01aH10,S03aH02,S01aH08,S02aH08,S02aH09,S04aH09,S05aH01,S03aH08,S03aH10,S06aH08,S01aH09,S03aH09,S05aH09,S03aH01</v>
+        <v>S02aH09,S04aH09,S05aH01,S02aH02,S04aH10,S06aH10,S01aH10,S03aH02,S04aH08,S06aH01,S01aH09,S03aH08,S03aH10,S06aH08,S01aH01,S04aH01,S06aH02,S04aH02,S01aH02,S05aH10,S02aH01,S02aH10,S05aH02,S05aH08,S03aH09,S05aH09,S03aH01,S06aH09,S01aH08,S02aH08</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S01aH06,S02aH03,S05aH07,S05aH08,S04aH05,S04aH08,S03aH03,S04aH03,S03aH02,S04aH06,S05aH04,S06aH02,S06aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S04aH02,S01aH02,S04aH04,S03aH04,S01aH03,S05aH02,S05aH03,S05aH06,S02aH04,S02aH05,S06aH07,S01aH04,S01aH07,S02aH07,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S02aH02,S06aH06</v>
+        <v>S03aH04,S03aH03,S04aH02,S05aH08,S01aH04,S01aH07,S02aH07,S02aH04,S02aH05,S06aH07,S01aH06,S02aH03,S05aH07,S03aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S04aH03,S04aH05,S04aH08,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S02aH02,S06aH06,S01aH03,S05aH02,S05aH03,S05aH06,S04aH06,S05aH04,S06aH02,S06aH03,S01aH02,S04aH04</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1456,7 +1456,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FD0CC3E-016B-411F-BB7A-4F924C8D011A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3070F8D-AFCF-45AB-AC28-4CCA12450182}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1596,7 +1596,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C756F0F9-A6FC-4D7A-A2F3-6646B4598FC1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A74AD581-5269-45E2-93AB-DC9040EFC3F6}">
   <dimension ref="B9:O1210"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -40058,7 +40058,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B832D3E-26C2-4164-B814-E879A42763DA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1D57660-CDD6-462C-92E2-1AC510EFA0A7}">
   <dimension ref="B9:IV60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -61111,7 +61111,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54815814-6916-4695-A6C7-DC60C96D0AAB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7780F44F-9FB5-43DC-834D-E73747F75D08}">
   <dimension ref="A9:S184"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_60.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_60.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11B25219-DD43-42C0-9A4F-A8B504FBDBE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA08D8AA-AF7D-4FB1-AAD2-ABFBC4360EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -741,13 +741,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S02aH04,S02aH05,S06aH07,S01aH02,S04aH04,S03aH04,S03aH03,S05aH08,S04aH05,S04aH08,S04aH06,S05aH04,S06aH02,S06aH03,S01aH04,S01aH07,S02aH07,S04aH03,S01aH06,S02aH03,S05aH07,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S02aH02,S06aH06,S01aH03,S05aH02,S05aH03,S05aH06,S04aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S03aH02</t>
+    <t>S01aH04,S01aH07,S02aH07,S03aH03,S04aH02,S03aH02,S02aH04,S02aH05,S06aH07,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S05aH08,S03aH04,S02aH02,S06aH06,S01aH06,S02aH03,S05aH07,S04aH05,S04aH08,S01aH03,S05aH02,S05aH03,S05aH06,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S01aH02,S04aH04,S04aH03,S04aH06,S05aH04,S06aH02,S06aH03</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S03aH08,S03aH10,S06aH08,S01aH08,S02aH08,S02aH09,S04aH09,S05aH01,S02aH02,S04aH10,S06aH10,S04aH08,S06aH01,S05aH08,S06aH09,S01aH09,S02aH01,S02aH10,S05aH02,S01aH01,S04aH01,S06aH02,S03aH09,S05aH09,S03aH01,S01aH10,S03aH02,S01aH02,S05aH10,S04aH02</t>
+    <t>S01aH09,S02aH02,S04aH10,S06aH10,S01aH10,S03aH02,S04aH02,S03aH08,S03aH10,S06aH08,S03aH09,S05aH09,S04aH08,S06aH01,S02aH09,S04aH09,S05aH01,S03aH01,S01aH01,S04aH01,S06aH02,S05aH08,S01aH02,S05aH10,S01aH08,S02aH08,S02aH01,S02aH10,S05aH02,S06aH09</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S03aH08,S03aH10,S06aH08,S01aH08,S02aH08,S02aH09,S04aH09,S05aH01,S02aH02,S04aH10,S06aH10,S04aH08,S06aH01,S05aH08,S06aH09,S01aH09,S02aH01,S02aH10,S05aH02,S01aH01,S04aH01,S06aH02,S03aH09,S05aH09,S03aH01,S01aH10,S03aH02,S01aH02,S05aH10,S04aH02</v>
+        <v>S01aH09,S02aH02,S04aH10,S06aH10,S01aH10,S03aH02,S04aH02,S03aH08,S03aH10,S06aH08,S03aH09,S05aH09,S04aH08,S06aH01,S02aH09,S04aH09,S05aH01,S03aH01,S01aH01,S04aH01,S06aH02,S05aH08,S01aH02,S05aH10,S01aH08,S02aH08,S02aH01,S02aH10,S05aH02,S06aH09</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S02aH04,S02aH05,S06aH07,S01aH02,S04aH04,S03aH04,S03aH03,S05aH08,S04aH05,S04aH08,S04aH06,S05aH04,S06aH02,S06aH03,S01aH04,S01aH07,S02aH07,S04aH03,S01aH06,S02aH03,S05aH07,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S02aH02,S06aH06,S01aH03,S05aH02,S05aH03,S05aH06,S04aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S03aH02</v>
+        <v>S01aH04,S01aH07,S02aH07,S03aH03,S04aH02,S03aH02,S02aH04,S02aH05,S06aH07,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S05aH08,S03aH04,S02aH02,S06aH06,S01aH06,S02aH03,S05aH07,S04aH05,S04aH08,S01aH03,S05aH02,S05aH03,S05aH06,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S01aH02,S04aH04,S04aH03,S04aH06,S05aH04,S06aH02,S06aH03</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1456,7 +1456,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8B91EB5-CD3D-450F-8C80-209C8CE83CD4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B04EADB9-1582-4061-A177-CADC74EF3DC9}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1596,7 +1596,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57B552AE-E173-4A6B-BD1B-864C516BA8B2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{228A3907-83A0-4B64-8348-E77FC0C82B5F}">
   <dimension ref="B9:O1210"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -40058,7 +40058,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BE96D58-3366-4D9D-B95E-72C59D9569E8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA5DCBB0-B297-4992-B131-3876049EFF4D}">
   <dimension ref="B9:IV60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -61111,7 +61111,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED488E4C-9092-4472-8B4F-4DEF5AE899C2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{644F3A63-2DB1-4D39-BF9A-2412AFF449AA}">
   <dimension ref="A9:S184"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_60.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_60.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4649C10-576D-4E8C-BEA6-CB1A490C0B0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{202C2EFF-4360-4B15-A99B-6CE499144DBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -765,13 +765,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S01aH02,S04aH04,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S04aH02,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S04aH05,S04aH08,S02aH02,S06aH06,S01aH04,S01aH07,S02aH07,S04aH03,S01aH03,S05aH02,S05aH03,S05aH06,S04aH06,S05aH04,S06aH02,S06aH03,S03aH04,S03aH02,S03aH03,S02aH04,S02aH05,S06aH07,S01aH06,S02aH03,S05aH07,S05aH08</t>
+    <t>S01aH04,S01aH07,S02aH07,S02aH02,S06aH06,S03aH03,S04aH06,S05aH04,S06aH02,S06aH03,S01aH02,S04aH04,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S02aH04,S02aH05,S06aH07,S01aH03,S05aH02,S05aH03,S05aH06,S03aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S03aH04,S04aH03,S04aH02,S05aH08,S01aH06,S02aH03,S05aH07,S04aH05,S04aH08</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S01aH08,S02aH08,S01aH02,S05aH10,S01aH10,S03aH02,S03aH09,S05aH09,S05aH08,S03aH01,S01aH09,S02aH01,S02aH10,S05aH02,S06aH09,S02aH09,S04aH09,S05aH01,S04aH02,S02aH02,S04aH10,S06aH10,S03aH08,S03aH10,S06aH08,S01aH01,S04aH01,S06aH02,S04aH08,S06aH01</t>
+    <t>S01aH09,S03aH01,S02aH02,S04aH10,S06aH10,S06aH09,S01aH08,S02aH08,S03aH09,S05aH09,S03aH08,S03aH10,S06aH08,S04aH02,S01aH02,S05aH10,S02aH09,S04aH09,S05aH01,S02aH01,S02aH10,S05aH02,S01aH10,S03aH02,S04aH08,S06aH01,S01aH01,S04aH01,S06aH02,S05aH08</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S01aH08,S02aH08,S01aH02,S05aH10,S01aH10,S03aH02,S03aH09,S05aH09,S05aH08,S03aH01,S01aH09,S02aH01,S02aH10,S05aH02,S06aH09,S02aH09,S04aH09,S05aH01,S04aH02,S02aH02,S04aH10,S06aH10,S03aH08,S03aH10,S06aH08,S01aH01,S04aH01,S06aH02,S04aH08,S06aH01</v>
+        <v>S01aH09,S03aH01,S02aH02,S04aH10,S06aH10,S06aH09,S01aH08,S02aH08,S03aH09,S05aH09,S03aH08,S03aH10,S06aH08,S04aH02,S01aH02,S05aH10,S02aH09,S04aH09,S05aH01,S02aH01,S02aH10,S05aH02,S01aH10,S03aH02,S04aH08,S06aH01,S01aH01,S04aH01,S06aH02,S05aH08</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S01aH02,S04aH04,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S04aH02,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S04aH05,S04aH08,S02aH02,S06aH06,S01aH04,S01aH07,S02aH07,S04aH03,S01aH03,S05aH02,S05aH03,S05aH06,S04aH06,S05aH04,S06aH02,S06aH03,S03aH04,S03aH02,S03aH03,S02aH04,S02aH05,S06aH07,S01aH06,S02aH03,S05aH07,S05aH08</v>
+        <v>S01aH04,S01aH07,S02aH07,S02aH02,S06aH06,S03aH03,S04aH06,S05aH04,S06aH02,S06aH03,S01aH02,S04aH04,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S02aH04,S02aH05,S06aH07,S01aH03,S05aH02,S05aH03,S05aH06,S03aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S03aH04,S04aH03,S04aH02,S05aH08,S01aH06,S02aH03,S05aH07,S04aH05,S04aH08</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1496,7 +1496,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E36D851B-EF46-489E-8D77-A160A1473A4A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFBE1566-A4B6-456B-8E05-C647A30A7176}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1636,7 +1636,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5245638E-26EE-4EDA-9AF4-2629957CCE89}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67C678BD-3043-4E95-AC11-DDFAB5659B0F}">
   <dimension ref="B9:O1210"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -40098,7 +40098,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E47DFCAF-DBA9-447F-B0AB-3B730F07E08A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55896B0F-C671-42AF-85D3-F98F210EB6C6}">
   <dimension ref="B9:LO60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -88171,7 +88171,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AFBC675-0083-41B0-BAD2-A3DED91AC3A3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{710A44E9-D567-45E9-85A5-125C4F34105A}">
   <dimension ref="A9:S184"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_60.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_TSParameters_ts_60.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ABF91F6-07FE-4B22-86AB-219D0AE89DE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B22D7B8-E93F-424C-8819-B575A259F447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -765,13 +765,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S01aH03,S05aH02,S05aH03,S05aH06,S04aH02,S04aH03,S03aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S03aH02,S02aH02,S06aH06,S01aH02,S04aH04,S04aH06,S05aH04,S06aH02,S06aH03,S01aH04,S01aH07,S02aH07,S03aH04,S05aH08,S04aH05,S04aH08,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S02aH04,S02aH05,S06aH07,S01aH06,S02aH03,S05aH07</t>
+    <t>S01aH04,S01aH07,S02aH07,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S05aH08,S02aH04,S02aH05,S06aH07,S04aH02,S01aH03,S05aH02,S05aH03,S05aH06,S01aH02,S04aH04,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S03aH02,S04aH03,S04aH06,S05aH04,S06aH02,S06aH03,S02aH02,S06aH06,S01aH06,S02aH03,S05aH07,S04aH05,S04aH08,S03aH04,S03aH03</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S01aH10,S03aH02,S02aH01,S02aH10,S05aH02,S02aH02,S04aH10,S06aH10,S01aH02,S05aH10,S04aH02,S03aH01,S01aH08,S02aH08,S06aH09,S01aH09,S02aH09,S04aH09,S05aH01,S04aH08,S06aH01,S05aH08,S03aH09,S05aH09,S03aH08,S03aH10,S06aH08,S01aH01,S04aH01,S06aH02</t>
+    <t>S01aH09,S01aH02,S05aH10,S04aH08,S06aH01,S03aH08,S03aH10,S06aH08,S01aH10,S03aH02,S01aH08,S02aH08,S03aH09,S05aH09,S04aH02,S02aH01,S02aH10,S05aH02,S06aH09,S03aH01,S01aH01,S04aH01,S06aH02,S05aH08,S02aH09,S04aH09,S05aH01,S02aH02,S04aH10,S06aH10</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S01aH10,S03aH02,S02aH01,S02aH10,S05aH02,S02aH02,S04aH10,S06aH10,S01aH02,S05aH10,S04aH02,S03aH01,S01aH08,S02aH08,S06aH09,S01aH09,S02aH09,S04aH09,S05aH01,S04aH08,S06aH01,S05aH08,S03aH09,S05aH09,S03aH08,S03aH10,S06aH08,S01aH01,S04aH01,S06aH02</v>
+        <v>S01aH09,S01aH02,S05aH10,S04aH08,S06aH01,S03aH08,S03aH10,S06aH08,S01aH10,S03aH02,S01aH08,S02aH08,S03aH09,S05aH09,S04aH02,S02aH01,S02aH10,S05aH02,S06aH09,S03aH01,S01aH01,S04aH01,S06aH02,S05aH08,S02aH09,S04aH09,S05aH01,S02aH02,S04aH10,S06aH10</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S01aH03,S05aH02,S05aH03,S05aH06,S04aH02,S04aH03,S03aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S03aH02,S02aH02,S06aH06,S01aH02,S04aH04,S04aH06,S05aH04,S06aH02,S06aH03,S01aH04,S01aH07,S02aH07,S03aH04,S05aH08,S04aH05,S04aH08,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S02aH04,S02aH05,S06aH07,S01aH06,S02aH03,S05aH07</v>
+        <v>S01aH04,S01aH07,S02aH07,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S05aH08,S02aH04,S02aH05,S06aH07,S04aH02,S01aH03,S05aH02,S05aH03,S05aH06,S01aH02,S04aH04,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S03aH02,S04aH03,S04aH06,S05aH04,S06aH02,S06aH03,S02aH02,S06aH06,S01aH06,S02aH03,S05aH07,S04aH05,S04aH08,S03aH04,S03aH03</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1496,7 +1496,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0E1FEC6-886B-49F7-801F-F79DA8A1D550}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B5F9C8A-5E0B-4237-8AE2-2D6ECE977A68}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1636,7 +1636,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70A75EED-E201-467E-AA09-95DCDB92A01F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACD7349D-A23A-4903-BE59-A82F906C098D}">
   <dimension ref="B9:O1210"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -40098,7 +40098,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28B8BB8B-286D-4311-829A-C4C9FBA8CB81}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A552251A-EB85-4416-A8FA-71776EBAE4A5}">
   <dimension ref="B9:LO60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -88171,7 +88171,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{763761D2-CC4E-4DC6-93EC-2DB1AF119FD6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{886AF859-D45D-411E-8612-A1F560DDB758}">
   <dimension ref="A9:S184"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
